--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_biobio.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_biobio.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 13:49</t>
+    <t xml:space="preserve">2026-09-09 20:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_biobio.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_biobio.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:12</t>
+    <t xml:space="preserve">2026-09-18 17:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_biobio.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_biobio.xlsx
@@ -30,105 +30,105 @@
     <t xml:space="preserve">Cobertura</t>
   </si>
   <si>
+    <t xml:space="preserve">Negrete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santa Juana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tucapel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quilaco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alto Biobío</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Rosendo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Alamos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contulmo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yumbel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antuco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Florida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santa Bárbara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cabrero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hualqui</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curanilahue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quilleco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mulchén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tirúa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tomé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Penco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Angeles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arauco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lebu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nacimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chiguayante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cañete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coronel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hualpén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talcahuano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concepción</t>
+  </si>
+  <si>
     <t xml:space="preserve">San Pedro de la Paz</t>
   </si>
   <si>
-    <t xml:space="preserve">Concepción</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talcahuano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hualpén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coronel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cañete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chiguayante</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nacimiento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lebu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arauco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Angeles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Penco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tomé</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tirúa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mulchén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quilleco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curanilahue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hualqui</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cabrero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santa Bárbara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Florida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antuco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yumbel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contulmo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Alamos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Rosendo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alto Biobío</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quilaco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tucapel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santa Juana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Negrete</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 17:06</t>
+    <t xml:space="preserve">2026-09-27 21:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -558,13 +558,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>138188</v>
+        <v>13018</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>151833</v>
+        <v>10539</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>91.01</v>
+        <v>123.52</v>
       </c>
     </row>
     <row r="3">
@@ -572,13 +572,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>228349</v>
+        <v>17554</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>239443</v>
+        <v>14870</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>95.37</v>
+        <v>118.05</v>
       </c>
     </row>
     <row r="4">
@@ -586,13 +586,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>153148</v>
+        <v>17642</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>158222</v>
+        <v>15379</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>96.79</v>
+        <v>114.71</v>
       </c>
     </row>
     <row r="5">
@@ -600,13 +600,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>95175</v>
+        <v>4760</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>97902</v>
+        <v>4187</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>97.21</v>
+        <v>113.69</v>
       </c>
     </row>
     <row r="6">
@@ -614,13 +614,13 @@
         <v>8</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>125854</v>
+        <v>7637</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>128253</v>
+        <v>6803</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>98.13</v>
+        <v>112.26</v>
       </c>
     </row>
     <row r="7">
@@ -628,13 +628,13 @@
         <v>9</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>36893</v>
+        <v>3990</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>37349</v>
+        <v>3565</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>98.78</v>
+        <v>111.92</v>
       </c>
     </row>
     <row r="8">
@@ -642,13 +642,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>91088</v>
+        <v>25439</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>91805</v>
+        <v>22856</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>99.22</v>
+        <v>111.3</v>
       </c>
     </row>
     <row r="9">
@@ -656,13 +656,13 @@
         <v>11</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>28146</v>
+        <v>7068</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>28016</v>
+        <v>6351</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>100.46</v>
+        <v>111.29</v>
       </c>
     </row>
     <row r="10">
@@ -670,13 +670,13 @@
         <v>12</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>27520</v>
+        <v>24601</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>27146</v>
+        <v>22194</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>101.38</v>
+        <v>110.85</v>
       </c>
     </row>
     <row r="11">
@@ -684,13 +684,13 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>39535</v>
+        <v>4766</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>38890</v>
+        <v>4322</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>101.66</v>
+        <v>110.27</v>
       </c>
     </row>
     <row r="12">
@@ -698,13 +698,13 @@
         <v>14</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>226394</v>
+        <v>12937</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>222593</v>
+        <v>11868</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>101.71</v>
+        <v>109.01</v>
       </c>
     </row>
     <row r="13">
@@ -712,13 +712,13 @@
         <v>15</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>51092</v>
+        <v>15915</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>50125</v>
+        <v>14657</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>101.93</v>
+        <v>108.58</v>
       </c>
     </row>
     <row r="14">
@@ -726,13 +726,13 @@
         <v>16</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>60265</v>
+        <v>25831</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>59069</v>
+        <v>23913</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>102.02</v>
+        <v>108.02</v>
       </c>
     </row>
     <row r="15">
@@ -740,13 +740,13 @@
         <v>17</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>47286</v>
+        <v>33453</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>45490</v>
+        <v>31023</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>103.95</v>
+        <v>107.83</v>
       </c>
     </row>
     <row r="16">
@@ -754,13 +754,13 @@
         <v>18</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>11537</v>
+        <v>28524</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>11088</v>
+        <v>26632</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>104.05</v>
+        <v>107.1</v>
       </c>
     </row>
     <row r="17">
@@ -768,13 +768,13 @@
         <v>19</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>32662</v>
+        <v>35934</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>31109</v>
+        <v>33938</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>104.99</v>
+        <v>105.88</v>
       </c>
     </row>
     <row r="18">
@@ -796,13 +796,13 @@
         <v>21</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>35934</v>
+        <v>32662</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>33938</v>
+        <v>31109</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>105.88</v>
+        <v>104.99</v>
       </c>
     </row>
     <row r="20">
@@ -810,13 +810,13 @@
         <v>22</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>28524</v>
+        <v>11537</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>26632</v>
+        <v>11088</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>107.1</v>
+        <v>104.05</v>
       </c>
     </row>
     <row r="21">
@@ -824,13 +824,13 @@
         <v>23</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>33453</v>
+        <v>47286</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>31023</v>
+        <v>45490</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>107.83</v>
+        <v>103.95</v>
       </c>
     </row>
     <row r="22">
@@ -838,13 +838,13 @@
         <v>24</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>25831</v>
+        <v>60265</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>23913</v>
+        <v>59069</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>108.02</v>
+        <v>102.02</v>
       </c>
     </row>
     <row r="23">
@@ -852,13 +852,13 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>15915</v>
+        <v>51092</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>14657</v>
+        <v>50125</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>108.58</v>
+        <v>101.93</v>
       </c>
     </row>
     <row r="24">
@@ -866,13 +866,13 @@
         <v>26</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>12937</v>
+        <v>226394</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>11868</v>
+        <v>222593</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>109.01</v>
+        <v>101.71</v>
       </c>
     </row>
     <row r="25">
@@ -880,13 +880,13 @@
         <v>27</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>4766</v>
+        <v>39535</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>4322</v>
+        <v>38890</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>110.27</v>
+        <v>101.66</v>
       </c>
     </row>
     <row r="26">
@@ -894,13 +894,13 @@
         <v>28</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>24601</v>
+        <v>27520</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>22194</v>
+        <v>27146</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>110.85</v>
+        <v>101.38</v>
       </c>
     </row>
     <row r="27">
@@ -908,13 +908,13 @@
         <v>29</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>7068</v>
+        <v>28146</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>6351</v>
+        <v>28016</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>111.29</v>
+        <v>100.46</v>
       </c>
     </row>
     <row r="28">
@@ -922,13 +922,13 @@
         <v>30</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>25439</v>
+        <v>91088</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>22856</v>
+        <v>91805</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>111.3</v>
+        <v>99.22</v>
       </c>
     </row>
     <row r="29">
@@ -936,13 +936,13 @@
         <v>31</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>3990</v>
+        <v>36893</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>3565</v>
+        <v>37349</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>111.92</v>
+        <v>98.78</v>
       </c>
     </row>
     <row r="30">
@@ -950,13 +950,13 @@
         <v>32</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>7637</v>
+        <v>125854</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>6803</v>
+        <v>128253</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>112.26</v>
+        <v>98.13</v>
       </c>
     </row>
     <row r="31">
@@ -964,13 +964,13 @@
         <v>33</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>4760</v>
+        <v>95175</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>4187</v>
+        <v>97902</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>113.69</v>
+        <v>97.21</v>
       </c>
     </row>
     <row r="32">
@@ -978,13 +978,13 @@
         <v>34</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>17642</v>
+        <v>153148</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>15379</v>
+        <v>158222</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>114.71</v>
+        <v>96.79</v>
       </c>
     </row>
     <row r="33">
@@ -992,13 +992,13 @@
         <v>35</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>17554</v>
+        <v>228349</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>14870</v>
+        <v>239443</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>118.05</v>
+        <v>95.37</v>
       </c>
     </row>
     <row r="34">
@@ -1006,13 +1006,13 @@
         <v>36</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>13018</v>
+        <v>138188</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>10539</v>
+        <v>151833</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>123.52</v>
+        <v>91.01</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_biobio.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2023_biobio.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">San Rosendo</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Contulmo</t>
@@ -96,7 +96,7 @@
     <t xml:space="preserve">Penco</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Arauco</t>
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 21:53</t>
+    <t xml:space="preserve">2026-10-05 05:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
